--- a/rolodex/data/liste_recettes.xlsx
+++ b/rolodex/data/liste_recettes.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tania/Dropbox/Scientific_Data_Insights_myownproject/rolodex/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tania/Dropbox/Scientific_Data_Insights_myownproject/oziblue/oziblue/rolodex/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E715C437-6AF2-AC46-86D9-DA21144F6ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42CAE048-9ACB-B744-8847-E57877D38868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" tabRatio="500" xr2:uid="{5F4BB7EB-844D-4444-B2C7-47CBECC6793D}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" tabRatio="500" xr2:uid="{2A4252C9-73E0-7D4F-AD3F-59EDD8EEF8BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="145621" concurrentCalc="0"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="621">
   <si>
     <t>Arepa carne desmechada</t>
   </si>
@@ -58,9 +69,6 @@
     <t>Online</t>
   </si>
   <si>
-    <t>Bacon -wrapped brussel sprouts</t>
-  </si>
-  <si>
     <t>Dropbox/Recettes and Food Network</t>
   </si>
   <si>
@@ -229,12 +237,6 @@
     <t>Fish</t>
   </si>
   <si>
-    <t>Livre orange de Cindy</t>
-  </si>
-  <si>
-    <t>Soupe de poulet au coco</t>
-  </si>
-  <si>
     <t>Carne con cebolla larga</t>
   </si>
   <si>
@@ -262,12 +264,6 @@
     <t>Ree Drummond The pioneer woman</t>
   </si>
   <si>
-    <t>Shepard Pie</t>
-  </si>
-  <si>
-    <t>Pâtes au saumon</t>
-  </si>
-  <si>
     <t>Truites au four</t>
   </si>
   <si>
@@ -280,9 +276,6 @@
     <t>Empanadas</t>
   </si>
   <si>
-    <t>Tranches panées</t>
-  </si>
-  <si>
     <t>Veal</t>
   </si>
   <si>
@@ -343,15 +336,9 @@
     <t>Hummus: 2 garlic cloves, 1 cup chickpeas, 0.75 tsp salt, 1/6 cup tahini, 3 tbs lemon juice, 1 tbs water or oil</t>
   </si>
   <si>
-    <t>Foodnetwork saves Viande board</t>
-  </si>
-  <si>
     <t>Chicken pot pie</t>
   </si>
   <si>
-    <t>Bœuf stroganof</t>
-  </si>
-  <si>
     <t>Asie</t>
   </si>
   <si>
@@ -409,9 +396,6 @@
     <t xml:space="preserve">Pains pitas fourrés </t>
   </si>
   <si>
-    <t>Fourré avec legumes, poulet, sauce yogurt</t>
-  </si>
-  <si>
     <t>Fondue chinoise de poisson</t>
   </si>
   <si>
@@ -424,9 +408,6 @@
     <t>Classeur de recettes bleu clair</t>
   </si>
   <si>
-    <t>Pesto chicken</t>
-  </si>
-  <si>
     <t>Food network magazine insert - 50 Chicken dinners n°19</t>
   </si>
   <si>
@@ -466,9 +447,6 @@
     <t>Rouleaux d'été</t>
   </si>
   <si>
-    <t>Avec feuille de riz: garnir avec crevettes, poisson, poulet, pousses de soja, legumes, sauces soja</t>
-  </si>
-  <si>
     <t>Fooby</t>
   </si>
   <si>
@@ -511,9 +489,6 @@
     <t>A baker's life, livre kindle Paul Hollywood</t>
   </si>
   <si>
-    <t>Sheet pan fajitas</t>
-  </si>
-  <si>
     <t>Food Network App " Mexicain" Board</t>
   </si>
   <si>
@@ -583,15 +558,9 @@
     <t>Saucisson et saucisse au chou</t>
   </si>
   <si>
-    <t>Qyfte qebapa / köfte / qofte dans pain pita</t>
-  </si>
-  <si>
     <t>Agneau</t>
   </si>
   <si>
-    <t>Boulettes de viande hachée d'agneau assaisonnée au bouillon de légumes et paprika</t>
-  </si>
-  <si>
     <t>Kosovo</t>
   </si>
   <si>
@@ -1435,20 +1404,503 @@
     <t>Sauce</t>
   </si>
   <si>
-    <t>Low GI</t>
-  </si>
-  <si>
-    <t>https://www.foodnetwork.com/recipes/aarti-sequeira/korean-inspired-ground-beef-lettuce-wraps-8030164</t>
+    <t>Soupe de maïs/mais au poulet</t>
+  </si>
+  <si>
+    <t>Livre Betty Bossi déchetterie "Spécialités orientales" p.10 (?)</t>
+  </si>
+  <si>
+    <t>Ajouter du pak choy</t>
+  </si>
+  <si>
+    <t>Satay de poulet et salade de concombre</t>
+  </si>
+  <si>
+    <t>Livre Betty Bossi déchetterie "Spécialités orientales" p.20</t>
+  </si>
+  <si>
+    <t>Canard aux légumes sautés</t>
+  </si>
+  <si>
+    <t>Duck</t>
+  </si>
+  <si>
+    <t>Livre Betty Bossi déchetterie "Spécialités orientales" p.36</t>
+  </si>
+  <si>
+    <t>Halloumi grillé, œufs durs, salade</t>
+  </si>
+  <si>
+    <t>Lemon garlic fish with cabbage slow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Season white fish fillet and pan fry. Season fish with garlic and ginger. Make a slaw with cabbage, carrot, onion, lettuce, lime juice and olive oil. </t>
+  </si>
+  <si>
+    <t>Bao zi</t>
+  </si>
+  <si>
+    <t>Recettes du cours de cuisine de Mati</t>
+  </si>
+  <si>
+    <t>Farcir avec de la saucisse de porc défaite et des légumes (oignon, chou chinois)</t>
+  </si>
+  <si>
+    <t>Cordon bleu</t>
+  </si>
+  <si>
+    <t>Courgettes farcies</t>
+  </si>
+  <si>
+    <t>Photocopie livre bibliothèque la cuisine libanaise</t>
+  </si>
+  <si>
+    <t>Sandwich de kefta</t>
+  </si>
+  <si>
+    <t>Servir avec de la tresse</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/29091/sandwich-de-kefta</t>
+  </si>
+  <si>
+    <t>Salmon con pasta de arroz y wasabi</t>
+  </si>
+  <si>
+    <t>Livre "1001 recetas de cocina sana" p.77</t>
+  </si>
+  <si>
+    <t>Croustade de pommes de terre au four et saumon fumé</t>
+  </si>
+  <si>
+    <t>cahier spirale "croustade de pommes de terre"</t>
+  </si>
+  <si>
+    <t>Tagliatelle à la féra fumée</t>
+  </si>
+  <si>
+    <t>Livre photocopié "Recettes du lac par Manu et son équipage"</t>
+  </si>
+  <si>
+    <t>Salmon bowl</t>
+  </si>
+  <si>
+    <t>Saumon, brocoli, fenouil, pousse de soja</t>
+  </si>
+  <si>
+    <t>Bacon, potato leek bake</t>
+  </si>
+  <si>
+    <t>Acorn squash with pomegranate and kale tabbouleh</t>
+  </si>
+  <si>
+    <t>Cooking Light Magazine Holiday cookbook Nov. 2015 p.12</t>
+  </si>
+  <si>
+    <t>Remplacer le squash par des courgettes et farcir avec du couscous</t>
+  </si>
+  <si>
+    <t>Chicken shish kebab and naan</t>
+  </si>
+  <si>
+    <t>BBC good food website, Dropbox pdf recettes</t>
+  </si>
+  <si>
+    <t>Cahier papillon, BBC good food website, Dropbox pdf recettes</t>
+  </si>
+  <si>
+    <t>Tourte aux blettes</t>
+  </si>
+  <si>
+    <t>Livre la cuisine mediterranéene, p.244</t>
+  </si>
+  <si>
+    <t>Fettucine with carrots and peppers</t>
+  </si>
+  <si>
+    <t>Food Network Magazine Pasta cookbook Aug 2024 p.49</t>
+  </si>
+  <si>
+    <t>Asian cucumber salad</t>
+  </si>
+  <si>
+    <t>Reverse-seared grilled chicken with piccatta butter</t>
+  </si>
+  <si>
+    <t>Food Network Magazine BBQ Time Jun-July 2024(?) p.69</t>
+  </si>
+  <si>
+    <t>Moroccan-spiced chicken sliders</t>
+  </si>
+  <si>
+    <t>Magazine Taste of Home, Summer cookouts &amp; potlucks, August 2025 p.16</t>
+  </si>
+  <si>
+    <t>Southwestern fattoush salad with black beans</t>
+  </si>
+  <si>
+    <t>Cooking Light Magazine, Digital Issue, Winter 2024, screenshot old Kindle</t>
+  </si>
+  <si>
+    <t>Galettes de pommes de terre au jambon</t>
+  </si>
+  <si>
+    <t>Fooby App Board Favoris et Petit déjeuner</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/27573/galettes-de-pommes-de-terre-au-jambon</t>
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>Kimbap</t>
+  </si>
+  <si>
+    <t>Fooby App Board world_food</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/28332/kimbap--gimbap-</t>
+  </si>
+  <si>
+    <t>Sushi coréen à la viande, omelette, etc</t>
+  </si>
+  <si>
+    <t>Grilled salmon salad</t>
+  </si>
+  <si>
+    <t>Cooking Light Magazine digital (Spring 2026) p.44 (High protein, vol 39 issue 1)</t>
+  </si>
+  <si>
+    <t>Crispy chicken rice bowl</t>
+  </si>
+  <si>
+    <t>Cooking Light Magazine digital (Spring 2026) p.54 (High protein, vol 39 issue 1)</t>
+  </si>
+  <si>
+    <t>Chicken and vegetable stir-fry with udon noodles</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/anne-burrell/chicken-and-vegetable-stir-fry-with-udon-noodles-3128962</t>
+  </si>
+  <si>
+    <t>Carnet de Sophie, légumes p.102, FN Magazine, Pasta cookbook, Aug. 2024, p.87</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/food-network-kitchen/asian-cucumber-salad-3363961</t>
+  </si>
+  <si>
+    <t>https://www.auxdelicesdupalais.net/article-maklouba-ma-loubeh-recette-syrienne-aux-aubergines-119618876.html</t>
+  </si>
+  <si>
+    <t>https://www.mycolombianrecipes.com/shredded-meat-carne-desmechada/</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/mochiko-chicken-5450542</t>
+  </si>
+  <si>
+    <t>Bacon-wrapped brussel sprouts</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/food-network-kitchen/bacon-wrapped-brussels-sprouts-with-creamy-lemon-dip-3364562</t>
+  </si>
+  <si>
+    <t>https://www.mycolombianrecipes.com/colombian-style-pork-risotto-arroz/</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/food-network-kitchen/chicken-kiev-recipe-2009050</t>
+  </si>
+  <si>
+    <t>https://www.theguardian.com/lifeandstyle/wordofmouth/2014/oct/02/how-to-make-perfect-naan-bread-recipe</t>
+  </si>
+  <si>
+    <t>https://globaltableadventure.com/recipe/recipe-central-asian-noodle-stew-lagman-shurpa/</t>
+  </si>
+  <si>
+    <t>https://www.bettybossi.ch/fr/recettes/recette/filets-de-fera-a-la-meuniere-10003993/</t>
+  </si>
+  <si>
+    <t>Carnet de Sophie</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/15049/tom-kha-gai</t>
+  </si>
+  <si>
+    <t>Soupe de poulet au coco, Tom Kha Gai</t>
+  </si>
+  <si>
+    <t>https://www.mycolombianrecipes.com/bistec-a-caballo-creole-steak-on-horseback/</t>
+  </si>
+  <si>
+    <t>https://www.mycolombianrecipes.com/colombian-chicken-sancocho-sancocho-de/</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/14328/quiche-au-fromage</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/17280/ramequins-au-fromage</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/17351/ceviche</t>
+  </si>
+  <si>
+    <t>https://blog.imusa.com.co/blog/imusa/recetas/sopa-de-papa-criolla/</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/11843/ragout-de-porc-sauce-moutarde</t>
+  </si>
+  <si>
+    <t>https://www.thepioneerwoman.com/food-cooking/recipes/a9886/egg-in-a-hole-see-alternate-names-below/</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/melissa-darabian/chicken-pot-pie-turnovers-recipe-1924003</t>
+  </si>
+  <si>
+    <t>Chicken Pot Pie Turnovers, Melissa D'Arabian</t>
+  </si>
+  <si>
+    <t>Shepherd Pie</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/melissa-darabian/shepherds-pie-recipe-1958464</t>
+  </si>
+  <si>
+    <t>https://www.swissmilk.ch/fr/recettes-idees/recettes/SM2021_W-CH_04/pates-au-saumon-fume/</t>
+  </si>
+  <si>
+    <t>Pâtes au saumon fumé</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/ree-drummond/beef-tacos-2632842</t>
+  </si>
+  <si>
+    <t>Tex mex</t>
+  </si>
+  <si>
+    <t>https://www.mycolombianrecipes.com/colombian-empanadas-empanadas-colombianas/</t>
+  </si>
+  <si>
+    <t>Use Yellow Arep'harina P.A.N</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/14239/escalope-viennoise</t>
+  </si>
+  <si>
+    <t>Tranches panées viennoises</t>
+  </si>
+  <si>
+    <t>https://iheartrecipes.com/southern-hush-puppies-recipe/</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/new-england-fish-chowder-recipe0-2117807</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/ina-garten/hummus-recipe-1940499</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/16669/saucisses-de-vienne-dans-une-pate-feuilletee</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/11222/bruschetta</t>
+  </si>
+  <si>
+    <t>https://little.fooby.ch/fr/recettes/19857/trio-de-crepes-salees</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/26613/crepes-croque-madame</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/ree-drummond/cinnamon-rolls-recipe-2125821</t>
+  </si>
+  <si>
+    <t>https://www.findbgfood.com/recipe-banitsa</t>
+  </si>
+  <si>
+    <t>Sandwich au homard</t>
+  </si>
+  <si>
+    <t>https://kellyneil.com/nova-scotia-lobster-roll/</t>
+  </si>
+  <si>
+    <t>Online recipe not the same as the one in Dropbox</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=-KKGdyNDTvA&amp;t=6s</t>
+  </si>
+  <si>
+    <t>Meat pie with mashed potato on the side and parsley gravy</t>
+  </si>
+  <si>
+    <t>Food network saves Viande board</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/rachael-ray/drop-biscuit-chicken-pot-pie-recipe-2200901</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/9940/boeuf-stroganov</t>
+  </si>
+  <si>
+    <t>Bœuf Stroganov</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/19197/potage-asiatique-au-bouilli?y=117&amp;x=0</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/23599/fricandeaux-a-la-viande-buf-</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/ree-drummond/baked-eggs-in-hash-brown-cups-recipe-1996102</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/ree-drummond/chicken-quesadillas-recipe-3645030</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/13907/raclette-a-la-montagnarde</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/14205/roestis</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/ina-garten/soppressata-and-cheese-in-puff-pastry-recipe-2106576</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/21083/soupe-asiatique</t>
+  </si>
+  <si>
+    <t>https://little.fooby.ch/fr/recettes/19886/pains-pita-farcis-</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/aarti-sequeira/tandoori-chicken-recipe-2118888</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/14152/fondue-de-poisson</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/articles/50-chicken-dinner-recipes</t>
+  </si>
+  <si>
+    <t>Pesto pasta and chicken</t>
+  </si>
+  <si>
+    <t>https://mesrecettesweck.com/recettes/salade-de-pois-chiches-a-litalienne/</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/19274/salade-d-orge-perle-aux-asperges-roties</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/26593/ragout-de-veau-aux-champignons</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/12217/saltimbocca-et-ble-dur-cremeux</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/18178/saltimbocca-de-truite-et-risotto-aux-courgettes</t>
+  </si>
+  <si>
+    <t>https://www.swissmilk.ch/fr/recettes-idees/recettes/LM201203_33/ragout-de-lapin-a-la-moutarde-et-a-la-creme/</t>
+  </si>
+  <si>
+    <t>Avec feuille de riz: garnir avec crevettes, poisson, poulet, pousses de soja, concombre, carottes, poivron, sauces soja</t>
+  </si>
+  <si>
+    <t>https://little.fooby.ch/fr/recettes/19486/rouleaux-d-ete-pour-les-enfants</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/food-network-kitchen/vietnamese-pork-and-green-bean-stir-fry-12360145</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/food-network-kitchen/pork-and-green-bean-stir-fry-with-ginger-cilantro-and-mint-4555112</t>
+  </si>
+  <si>
+    <t>https://www.allrecipes.com/recipe/259065/soy-marinated-pork-sandwiches/</t>
+  </si>
+  <si>
+    <t>Sheet pan chicken fajitas</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/food-network-kitchen/sheet-pan-chicken-fajitas-3680272</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/food-network-kitchen/baked-tilapia-with-coconut-cilantro-sauce-recipe-2106823</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reels/DYKkGdzt1W7/</t>
+  </si>
+  <si>
+    <t>Online recipe not the same as the one in paper notebook or magazine</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/food-network-kitchen/zucchini-parmesan-recipe-2268731</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/11245/polpette</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/food-network-kitchen/hot-pot-at-home-10016478</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/14527/papet-vaudois</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LzepJPYyEM0&amp;list=PLEt2c8Dk6TnEB1DIpkmbdeKN9lfXN8-uc&amp;index=8</t>
+  </si>
+  <si>
+    <t>Fourré avec legumes, poulet, sauce yogurt. Voir recette Youtube de Paul Hollywood pour fabriquer pain pitta</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WhTp6c3C0zE&amp;list=PLEt2c8Dk6TnEB1DIpkmbdeKN9lfXN8-uc&amp;index=5</t>
+  </si>
+  <si>
+    <t>Qyfte qebapa / köfte / qofte dans pain pita (pitta)</t>
+  </si>
+  <si>
+    <t>Boulettes de viande hachée d'agneau assaisonnée au bouillon de légumes et paprika. Voir recette de pain pitta de Paul Hollywood sur youtube</t>
+  </si>
+  <si>
+    <t>Petits pains à l'ail (pampushki)</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/27932/petits-pains-a-l-ail--pampushki-#</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/26315/tranches-au-fromage-a-l-ail-</t>
+  </si>
+  <si>
+    <t>Cahier de Sophie p.19</t>
+  </si>
+  <si>
+    <t>Online recipe not the same as the one in paper notebook</t>
+  </si>
+  <si>
+    <t>Alternativement, voir tranches de pain à l'ail sur Fooby</t>
+  </si>
+  <si>
+    <t>https://migusto.migros.ch/fr/recettes/filet-mignon-en-manteau-de-lard</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/19502/curry-de-chou-fleur-et-pommes-de-terre</t>
+  </si>
+  <si>
+    <t>https://www.bbcgoodfood.com/recipes/fattoush</t>
+  </si>
+  <si>
+    <t>https://fooby.ch/fr/recettes/17600/soupe-au-poulet-et-au-gingembre</t>
+  </si>
+  <si>
+    <t>https://www.foodnetwork.com/recipes/bobby-flay/bobby-flays-tostones-with-salmon-tartar-and-avocado-chipotle-relish-recipe-1949646</t>
+  </si>
+  <si>
+    <t>Utiliser la sauce Poke Bowl coop</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1460,6 +1912,13 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1486,9 +1945,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1896,8 +2356,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91E33D68-1351-A342-B502-AE4885A67D8D}">
-  <dimension ref="A1:G221"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C227BAE0-508C-4340-8B2F-FCCCC7BECEE0}">
+  <dimension ref="A1:G249"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.1640625" customWidth="1"/>
@@ -1906,25 +2366,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="F1" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="G1" t="s">
-        <v>473</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -1932,10 +2392,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -1943,7 +2406,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1960,7 +2423,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -1970,6 +2433,9 @@
       </c>
       <c r="E4" t="s">
         <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1977,7 +2443,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
@@ -1985,38 +2451,47 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>522</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
+      <c r="F6" s="1" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
         <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -2024,13 +2499,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -2038,27 +2513,30 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
+      <c r="F10" s="1" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
@@ -2066,1233 +2544,1476 @@
       <c r="E11" t="s">
         <v>10</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>526</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>32</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
         <v>34</v>
       </c>
-      <c r="E13" t="s">
-        <v>35</v>
+      <c r="F13" s="1" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>531</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>529</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>37</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
         <v>66</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>196</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>63</v>
+      </c>
+      <c r="E35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>542</v>
+      </c>
+      <c r="B39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>545</v>
+      </c>
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" t="s">
         <v>38</v>
       </c>
-      <c r="B17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>140</v>
-      </c>
-      <c r="B18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="F40" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>79</v>
+      </c>
+      <c r="B42" t="s">
         <v>66</v>
       </c>
-      <c r="D22" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="D42" t="s">
+        <v>547</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" t="s">
+        <v>549</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>551</v>
+      </c>
+      <c r="B44" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" t="s">
         <v>19</v>
       </c>
-      <c r="D23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>210</v>
-      </c>
-      <c r="B28" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" t="s">
-        <v>63</v>
-      </c>
-      <c r="E34" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" t="s">
-        <v>20</v>
-      </c>
-      <c r="D35" t="s">
-        <v>64</v>
-      </c>
-      <c r="E35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" t="s">
-        <v>74</v>
-      </c>
-      <c r="E36" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" t="s">
-        <v>66</v>
-      </c>
-      <c r="E37" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-      <c r="D38" t="s">
-        <v>78</v>
-      </c>
-      <c r="E38" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>80</v>
-      </c>
-      <c r="B39" t="s">
-        <v>66</v>
-      </c>
-      <c r="D39" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>81</v>
-      </c>
-      <c r="B40" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>82</v>
-      </c>
-      <c r="B41" t="s">
-        <v>68</v>
-      </c>
-      <c r="D41" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="D45" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>84</v>
-      </c>
-      <c r="B42" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" t="s">
-        <v>67</v>
-      </c>
-      <c r="D43" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" t="s">
-        <v>87</v>
-      </c>
-      <c r="D44" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" t="s">
-        <v>89</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F45" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F46" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D47" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F47" s="1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" t="s">
+        <v>33</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>91</v>
+      </c>
+      <c r="B50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" t="s">
+        <v>33</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>92</v>
+      </c>
+      <c r="B51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D51" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>93</v>
+      </c>
+      <c r="B52" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" t="s">
+        <v>74</v>
+      </c>
+      <c r="D53" t="s">
         <v>95</v>
-      </c>
-      <c r="B48" t="s">
-        <v>72</v>
-      </c>
-      <c r="D48" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B50" t="s">
-        <v>72</v>
-      </c>
-      <c r="D50" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>98</v>
-      </c>
-      <c r="B51" t="s">
-        <v>77</v>
-      </c>
-      <c r="D51" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>99</v>
-      </c>
-      <c r="B52" t="s">
-        <v>68</v>
-      </c>
-      <c r="D52" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>100</v>
-      </c>
-      <c r="B53" t="s">
-        <v>77</v>
-      </c>
-      <c r="D53" t="s">
-        <v>101</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F53" s="1" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" t="s">
+        <v>561</v>
+      </c>
+      <c r="D54" t="s">
+        <v>96</v>
+      </c>
+      <c r="E54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G54" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>98</v>
+      </c>
+      <c r="B55" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55" t="s">
+        <v>565</v>
+      </c>
+      <c r="D55" t="s">
+        <v>99</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>100</v>
+      </c>
+      <c r="B56" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>101</v>
+      </c>
+      <c r="B57" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" t="s">
+        <v>104</v>
+      </c>
+      <c r="D57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" t="s">
+        <v>566</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>569</v>
+      </c>
+      <c r="B58" t="s">
+        <v>66</v>
+      </c>
+      <c r="D58" t="s">
+        <v>570</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
         <v>103</v>
       </c>
-      <c r="B54" t="s">
-        <v>68</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="B59" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>104</v>
-      </c>
-      <c r="B55" t="s">
-        <v>67</v>
-      </c>
-      <c r="D55" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56" t="s">
-        <v>20</v>
-      </c>
-      <c r="D56" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>108</v>
-      </c>
-      <c r="B57" t="s">
-        <v>66</v>
-      </c>
-      <c r="C57" t="s">
-        <v>112</v>
-      </c>
-      <c r="D57" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>109</v>
-      </c>
-      <c r="B58" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>111</v>
-      </c>
-      <c r="B59" t="s">
-        <v>67</v>
-      </c>
-      <c r="D59" t="s">
-        <v>110</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F59" s="1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>105</v>
+      </c>
+      <c r="B60" t="s">
+        <v>66</v>
+      </c>
+      <c r="D60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>106</v>
+      </c>
+      <c r="B61" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" t="s">
+        <v>107</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>108</v>
+      </c>
+      <c r="B62" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62" t="s">
+        <v>44</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>109</v>
+      </c>
+      <c r="B63" t="s">
+        <v>110</v>
+      </c>
+      <c r="D63" t="s">
+        <v>33</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>111</v>
+      </c>
+      <c r="B64" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" t="s">
+        <v>112</v>
+      </c>
+      <c r="D64" t="s">
+        <v>33</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
         <v>113</v>
       </c>
-      <c r="B60" t="s">
-        <v>67</v>
-      </c>
-      <c r="D60" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+      <c r="B65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" t="s">
+        <v>33</v>
+      </c>
+      <c r="E65" t="s">
+        <v>222</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
         <v>114</v>
       </c>
-      <c r="B61" t="s">
-        <v>77</v>
-      </c>
-      <c r="D61" t="s">
-        <v>23</v>
-      </c>
-      <c r="E61" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+      <c r="B66" t="s">
+        <v>64</v>
+      </c>
+      <c r="D66" t="s">
         <v>116</v>
       </c>
-      <c r="B62" t="s">
-        <v>66</v>
-      </c>
-      <c r="D62" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+      <c r="E66" t="s">
         <v>117</v>
       </c>
-      <c r="B63" t="s">
+      <c r="F66" s="1" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>120</v>
+      </c>
+      <c r="B67" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" t="s">
+        <v>605</v>
+      </c>
+      <c r="D67" t="s">
+        <v>86</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
         <v>118</v>
       </c>
-      <c r="D63" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>119</v>
-      </c>
-      <c r="B64" t="s">
-        <v>20</v>
-      </c>
-      <c r="C64" t="s">
-        <v>120</v>
-      </c>
-      <c r="D64" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>121</v>
-      </c>
-      <c r="B65" t="s">
-        <v>72</v>
-      </c>
-      <c r="D65" t="s">
-        <v>34</v>
-      </c>
-      <c r="E65" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>122</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="B68" t="s">
         <v>65</v>
-      </c>
-      <c r="D66" t="s">
-        <v>124</v>
-      </c>
-      <c r="E66" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>128</v>
-      </c>
-      <c r="B67" t="s">
-        <v>66</v>
-      </c>
-      <c r="C67" t="s">
-        <v>129</v>
-      </c>
-      <c r="D67" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>126</v>
-      </c>
-      <c r="B68" t="s">
-        <v>66</v>
       </c>
       <c r="D68" t="s">
         <v>9</v>
       </c>
       <c r="E68" t="s">
+        <v>119</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>121</v>
+      </c>
+      <c r="B69" t="s">
+        <v>67</v>
+      </c>
+      <c r="D69" t="s">
+        <v>115</v>
+      </c>
+      <c r="E69" t="s">
+        <v>122</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>123</v>
+      </c>
+      <c r="B70" t="s">
+        <v>69</v>
+      </c>
+      <c r="D70" t="s">
+        <v>33</v>
+      </c>
+      <c r="E70" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>583</v>
+      </c>
+      <c r="B71" t="s">
+        <v>65</v>
+      </c>
+      <c r="D71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" t="s">
+        <v>125</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>126</v>
+      </c>
+      <c r="B72" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" t="s">
+        <v>33</v>
+      </c>
+      <c r="E72" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>130</v>
-      </c>
-      <c r="B69" t="s">
-        <v>68</v>
-      </c>
-      <c r="D69" t="s">
-        <v>123</v>
-      </c>
-      <c r="E69" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+      <c r="F72" s="1" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>128</v>
+      </c>
+      <c r="B73" t="s">
+        <v>67</v>
+      </c>
+      <c r="D73" t="s">
+        <v>33</v>
+      </c>
+      <c r="E73" t="s">
+        <v>129</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
         <v>132</v>
       </c>
-      <c r="B70" t="s">
-        <v>72</v>
-      </c>
-      <c r="D70" t="s">
-        <v>34</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="B74" t="s">
+        <v>66</v>
+      </c>
+      <c r="D74" t="s">
+        <v>33</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="B75" t="s">
+        <v>66</v>
+      </c>
+      <c r="D75" t="s">
+        <v>38</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
         <v>134</v>
       </c>
-      <c r="B71" t="s">
-        <v>66</v>
-      </c>
-      <c r="D71" t="s">
-        <v>23</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="B76" t="s">
+        <v>67</v>
+      </c>
+      <c r="D76" t="s">
+        <v>38</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
+      <c r="B77" t="s">
         <v>136</v>
       </c>
-      <c r="B72" t="s">
-        <v>20</v>
-      </c>
-      <c r="D72" t="s">
-        <v>34</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="D77" t="s">
+        <v>33</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+      <c r="B78" t="s">
+        <v>65</v>
+      </c>
+      <c r="C78" t="s">
+        <v>590</v>
+      </c>
+      <c r="D78" t="s">
+        <v>116</v>
+      </c>
+      <c r="E78" t="s">
         <v>138</v>
       </c>
-      <c r="B73" t="s">
-        <v>68</v>
-      </c>
-      <c r="D73" t="s">
-        <v>34</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="F78" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+      <c r="B79" t="s">
+        <v>65</v>
+      </c>
+      <c r="C79" t="s">
+        <v>141</v>
+      </c>
+      <c r="E79" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
         <v>142</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
+        <v>69</v>
+      </c>
+      <c r="D80" t="s">
+        <v>102</v>
+      </c>
+      <c r="E80" t="s">
+        <v>143</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>144</v>
+      </c>
+      <c r="B81" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>145</v>
+      </c>
+      <c r="B82" t="s">
         <v>67</v>
-      </c>
-      <c r="D74" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>143</v>
-      </c>
-      <c r="B75" t="s">
-        <v>67</v>
-      </c>
-      <c r="D75" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>144</v>
-      </c>
-      <c r="B76" t="s">
-        <v>68</v>
-      </c>
-      <c r="D76" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>145</v>
-      </c>
-      <c r="B77" t="s">
-        <v>146</v>
-      </c>
-      <c r="D77" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B78" t="s">
-        <v>66</v>
-      </c>
-      <c r="C78" t="s">
-        <v>148</v>
-      </c>
-      <c r="D78" t="s">
-        <v>124</v>
-      </c>
-      <c r="E78" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>150</v>
-      </c>
-      <c r="B79" t="s">
-        <v>66</v>
-      </c>
-      <c r="C79" t="s">
-        <v>152</v>
-      </c>
-      <c r="E79" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>153</v>
-      </c>
-      <c r="B80" t="s">
-        <v>72</v>
-      </c>
-      <c r="D80" t="s">
-        <v>110</v>
-      </c>
-      <c r="E80" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>155</v>
-      </c>
-      <c r="B81" t="s">
-        <v>20</v>
-      </c>
-      <c r="D81" t="s">
-        <v>15</v>
-      </c>
-      <c r="E81" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>156</v>
-      </c>
-      <c r="B82" t="s">
-        <v>68</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
       </c>
       <c r="E82" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>148</v>
+      </c>
+      <c r="B83" t="s">
+        <v>69</v>
+      </c>
+      <c r="D83" t="s">
+        <v>102</v>
+      </c>
+      <c r="E83" t="s">
+        <v>149</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>150</v>
+      </c>
+      <c r="B84" t="s">
+        <v>67</v>
+      </c>
+      <c r="D84" t="s">
+        <v>99</v>
+      </c>
+      <c r="E84" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>595</v>
+      </c>
+      <c r="B85" t="s">
+        <v>65</v>
+      </c>
+      <c r="D85" t="s">
+        <v>44</v>
+      </c>
+      <c r="E85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>153</v>
+      </c>
+      <c r="B86" t="s">
+        <v>67</v>
+      </c>
+      <c r="D86" t="s">
+        <v>22</v>
+      </c>
+      <c r="E86" t="s">
+        <v>154</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>155</v>
+      </c>
+      <c r="B87" t="s">
+        <v>65</v>
+      </c>
+      <c r="C87" t="s">
+        <v>156</v>
+      </c>
+      <c r="D87" t="s">
+        <v>102</v>
+      </c>
+      <c r="E87" t="s">
+        <v>157</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="G87" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+      <c r="B88" t="s">
         <v>159</v>
       </c>
-      <c r="B83" t="s">
-        <v>72</v>
-      </c>
-      <c r="D83" t="s">
-        <v>110</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="D88" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
+      <c r="B89" t="s">
         <v>161</v>
       </c>
-      <c r="B84" t="s">
-        <v>68</v>
-      </c>
-      <c r="D84" t="s">
-        <v>105</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="C89" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+      <c r="D89" t="s">
+        <v>38</v>
+      </c>
+      <c r="E89" t="s">
         <v>163</v>
       </c>
-      <c r="B85" t="s">
+      <c r="F89" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>164</v>
+      </c>
+      <c r="B90" t="s">
         <v>66</v>
       </c>
-      <c r="D85" t="s">
-        <v>45</v>
-      </c>
-      <c r="E85" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
+      <c r="C90" t="s">
         <v>165</v>
       </c>
-      <c r="B86" t="s">
-        <v>68</v>
-      </c>
-      <c r="D86" t="s">
-        <v>23</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="D90" t="s">
+        <v>38</v>
+      </c>
+      <c r="E90" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+      <c r="F90" s="1" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
         <v>167</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B91" t="s">
         <v>66</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D91" t="s">
+        <v>22</v>
+      </c>
+      <c r="E91" t="s">
         <v>168</v>
       </c>
-      <c r="D87" t="s">
-        <v>110</v>
-      </c>
-      <c r="E87" t="s">
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+      <c r="B92" t="s">
+        <v>66</v>
+      </c>
+      <c r="D92" t="s">
+        <v>115</v>
+      </c>
+      <c r="E92" t="s">
         <v>170</v>
       </c>
-      <c r="B88" t="s">
+      <c r="F92" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
         <v>171</v>
       </c>
-      <c r="D88" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+      <c r="B93" t="s">
+        <v>66</v>
+      </c>
+      <c r="D93" t="s">
+        <v>33</v>
+      </c>
+      <c r="E93" t="s">
         <v>172</v>
       </c>
-      <c r="B89" t="s">
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
         <v>173</v>
       </c>
-      <c r="C89" t="s">
+      <c r="B94" t="s">
+        <v>69</v>
+      </c>
+      <c r="D94" t="s">
+        <v>33</v>
+      </c>
+      <c r="E94" t="s">
         <v>174</v>
       </c>
-      <c r="D89" t="s">
-        <v>39</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="F94" s="1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>607</v>
+      </c>
+      <c r="B95" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
+      <c r="C95" t="s">
+        <v>608</v>
+      </c>
+      <c r="D95" t="s">
         <v>176</v>
       </c>
-      <c r="B90" t="s">
-        <v>67</v>
-      </c>
-      <c r="C90" t="s">
+      <c r="E95" t="s">
         <v>177</v>
       </c>
-      <c r="D90" t="s">
-        <v>39</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="F95" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
+      <c r="B96" t="s">
         <v>179</v>
       </c>
-      <c r="B91" t="s">
-        <v>67</v>
-      </c>
-      <c r="D91" t="s">
-        <v>23</v>
-      </c>
-      <c r="E91" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>181</v>
-      </c>
-      <c r="B92" t="s">
-        <v>67</v>
-      </c>
-      <c r="D92" t="s">
-        <v>123</v>
-      </c>
-      <c r="E92" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>183</v>
-      </c>
-      <c r="B93" t="s">
-        <v>67</v>
-      </c>
-      <c r="D93" t="s">
-        <v>34</v>
-      </c>
-      <c r="E93" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>185</v>
-      </c>
-      <c r="B94" t="s">
-        <v>72</v>
-      </c>
-      <c r="D94" t="s">
-        <v>34</v>
-      </c>
-      <c r="E94" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>187</v>
-      </c>
-      <c r="B95" t="s">
-        <v>188</v>
-      </c>
-      <c r="C95" t="s">
-        <v>189</v>
-      </c>
-      <c r="D95" t="s">
-        <v>190</v>
-      </c>
-      <c r="E95" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>192</v>
-      </c>
-      <c r="B96" t="s">
-        <v>193</v>
+      <c r="C96" t="s">
+        <v>614</v>
       </c>
       <c r="D96" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="E96" t="s">
+        <v>612</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="G96" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="B97" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C97" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E97" t="s">
-        <v>178</v>
+        <v>166</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B98" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E98" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B99" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D99" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E99" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="B100" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C100" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D100" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E100" t="s">
-        <v>201</v>
+        <v>187</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="B101" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D101" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="E101" t="s">
-        <v>205</v>
+        <v>191</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B102" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E102" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="B103" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D103" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E103" t="s">
-        <v>209</v>
+        <v>195</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B104" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E104" t="s">
-        <v>212</v>
+        <v>198</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="D105" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E105" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B106" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="C106" t="s">
+        <v>620</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
@@ -3300,1695 +4021,2187 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="B107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D107" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="B108" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E108" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="B109" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D109" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="E109" t="s">
-        <v>166</v>
-      </c>
-      <c r="F109" t="s">
-        <v>472</v>
+        <v>154</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B110" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E110" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="B111" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D111" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E111" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B112" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D112" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E112" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B113" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D113" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E113" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="B114" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E114" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="B115" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E115" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="B116" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D116" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E116" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="B117" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D117" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="E117" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="B118" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D118" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E118" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="B119" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D119" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E119" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="B120" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D120" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E120" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B121" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D121" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="B122" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D122" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E122" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B123" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D123" t="s">
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="B124" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D124" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="B125" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D125" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E125" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="B126" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C126" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D126" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E126" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="B127" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D127" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E127" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="B128" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C128" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="D128" t="s">
         <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="B129" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D129" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="E129" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B130" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="E130" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="B131" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D131" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E131" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="B132" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D132" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E132" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="B133" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D133" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="E133" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="B134" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D134" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E134" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="B135" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D135" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E135" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B136" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C136" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="D136" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E136" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="D137" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E137" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="B138" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D138" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E138" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="B139" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C139" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="D139" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E139" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="B140" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D140" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E140" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B141" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C141" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="D141" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E141" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="B142" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D142" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E142" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="B143" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C143" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="B144" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D144" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E144" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B145" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D145" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E145" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B146" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C146" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="D146" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E146" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="B147" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C147" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="D147" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E147" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="B148" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C148" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="D148" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E148" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="B149" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D149" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E149" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="B150" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D150" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E150" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="B151" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D151" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E151" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="B152" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C152" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="D152" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E152" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="B153" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="B154" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D154" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E154" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B155" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D155" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E155" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="B156" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D156" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E156" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="B157" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D157" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="B158" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D158" t="s">
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B159" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="C159" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D159" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E159" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="B160" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C160" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="D160" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E160" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B161" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C161" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="D161" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E161" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B162" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C162" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="D162" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E162" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="B163" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D163" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E163" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="B164" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D164" t="s">
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="B165" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D165" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E165" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="B166" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D166" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E166" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="B167" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D167" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E167" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="B168" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D168" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E168" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="B169" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D169" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="B170" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D170" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E170" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="B171" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="C171" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="D171" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E171" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="B172" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C172" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="D172" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E172" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="B173" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C173" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="D173" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E173" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="B174" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D174" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E174" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="B175" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D175" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="E175" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B176" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C176" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="D176" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="E176" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="B177" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D177" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E177" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B178" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D178" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E178" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="B179" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D179" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E179" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="B180" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D180" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E180" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="B181" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D181" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E181" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="B182" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D182" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E182" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B183" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D183" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E183" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="B184" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D184" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E184" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="B185" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C185" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="D185" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E185" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="B186" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D186" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E186" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="C187" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="D187" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E187" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="B188" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D188" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E188" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="B189" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D189" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E189" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="B190" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D190" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E190" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="B191" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D191" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E191" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="B192" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D192" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E192" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="B193" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D193" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E193" t="s">
-        <v>402</v>
+        <v>388</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="B194" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="D194" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="B195" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C195" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="D195" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E195" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="B196" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C196" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="D196" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E196" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="B197" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D197" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E197" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="B198" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D198" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E198" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="B199" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D199" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E199" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="B200" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D200" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E200" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="B201" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="D201" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E201" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="B202" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D202" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="E202" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="B203" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D203" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="E203" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="B204" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D204" t="s">
         <v>5</v>
       </c>
       <c r="E204" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="B205" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D205" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E205" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="B206" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D206" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="E206" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="B207" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D207" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E207" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D208" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E208" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D209" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="E209" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="B210" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D210" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E210" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="B211" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D211" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E211" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="B212" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C212" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="D212" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E212" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="B213" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D213" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E213" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="B214" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D214" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="E214" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="B215" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D215" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E215" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="B216" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D216" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="E216" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="B217" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D217" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E217" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="G217" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="B218" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D218" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E218" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="B219" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D219" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E219" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B220" t="s">
+        <v>65</v>
+      </c>
+      <c r="D220" t="s">
+        <v>22</v>
+      </c>
+      <c r="E220" t="s">
+        <v>76</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>457</v>
+      </c>
+      <c r="B221" t="s">
+        <v>312</v>
+      </c>
+      <c r="C221" t="s">
+        <v>459</v>
+      </c>
+      <c r="D221" t="s">
+        <v>102</v>
+      </c>
+      <c r="E221" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>460</v>
+      </c>
+      <c r="B222" t="s">
+        <v>65</v>
+      </c>
+      <c r="D222" t="s">
+        <v>102</v>
+      </c>
+      <c r="E222" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>462</v>
+      </c>
+      <c r="B223" t="s">
+        <v>463</v>
+      </c>
+      <c r="D223" t="s">
+        <v>102</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>465</v>
+      </c>
+      <c r="B224" t="s">
+        <v>216</v>
+      </c>
+      <c r="D224" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>466</v>
+      </c>
+      <c r="B225" t="s">
+        <v>67</v>
+      </c>
+      <c r="D225" t="s">
+        <v>22</v>
+      </c>
+      <c r="E225" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>468</v>
+      </c>
+      <c r="B226" t="s">
+        <v>69</v>
+      </c>
+      <c r="C226" t="s">
+        <v>470</v>
+      </c>
+      <c r="D226" t="s">
+        <v>115</v>
+      </c>
+      <c r="E226" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>471</v>
+      </c>
+      <c r="B227" t="s">
+        <v>69</v>
+      </c>
+      <c r="D227" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>472</v>
+      </c>
+      <c r="B228" t="s">
         <v>66</v>
       </c>
-      <c r="D220" t="s">
-        <v>23</v>
-      </c>
-      <c r="E220" t="s">
-        <v>79</v>
-      </c>
-      <c r="F220" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B221" t="s">
-        <v>471</v>
+      <c r="D228" t="s">
+        <v>86</v>
+      </c>
+      <c r="E228" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>474</v>
+      </c>
+      <c r="B229" t="s">
+        <v>66</v>
+      </c>
+      <c r="C229" t="s">
+        <v>475</v>
+      </c>
+      <c r="E229" t="s">
+        <v>380</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>477</v>
+      </c>
+      <c r="B230" t="s">
+        <v>67</v>
+      </c>
+      <c r="D230" t="s">
+        <v>102</v>
+      </c>
+      <c r="E230" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>479</v>
+      </c>
+      <c r="B231" t="s">
+        <v>67</v>
+      </c>
+      <c r="D231" t="s">
+        <v>33</v>
+      </c>
+      <c r="E231" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>481</v>
+      </c>
+      <c r="B232" t="s">
+        <v>67</v>
+      </c>
+      <c r="D232" t="s">
+        <v>33</v>
+      </c>
+      <c r="E232" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>483</v>
+      </c>
+      <c r="B233" t="s">
+        <v>67</v>
+      </c>
+      <c r="C233" t="s">
+        <v>484</v>
+      </c>
+      <c r="D233" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>485</v>
+      </c>
+      <c r="B234" t="s">
+        <v>69</v>
+      </c>
+      <c r="D234" t="s">
+        <v>99</v>
+      </c>
+      <c r="E234" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>486</v>
+      </c>
+      <c r="B235" t="s">
+        <v>216</v>
+      </c>
+      <c r="C235" t="s">
+        <v>488</v>
+      </c>
+      <c r="D235" t="s">
+        <v>86</v>
+      </c>
+      <c r="E235" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>489</v>
+      </c>
+      <c r="B236" t="s">
+        <v>65</v>
+      </c>
+      <c r="D236" t="s">
+        <v>9</v>
+      </c>
+      <c r="E236" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>492</v>
+      </c>
+      <c r="B237" t="s">
+        <v>66</v>
+      </c>
+      <c r="E237" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>494</v>
+      </c>
+      <c r="E238" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>496</v>
+      </c>
+      <c r="B239" t="s">
+        <v>19</v>
+      </c>
+      <c r="D239" t="s">
+        <v>102</v>
+      </c>
+      <c r="E239" t="s">
+        <v>517</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>497</v>
+      </c>
+      <c r="B240" t="s">
+        <v>65</v>
+      </c>
+      <c r="D240" t="s">
+        <v>22</v>
+      </c>
+      <c r="E240" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>499</v>
+      </c>
+      <c r="B241" t="s">
+        <v>65</v>
+      </c>
+      <c r="D241" t="s">
+        <v>412</v>
+      </c>
+      <c r="E241" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>501</v>
+      </c>
+      <c r="B242" t="s">
+        <v>216</v>
+      </c>
+      <c r="D242" t="s">
+        <v>86</v>
+      </c>
+      <c r="E242" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>503</v>
+      </c>
+      <c r="B243" t="s">
+        <v>74</v>
+      </c>
+      <c r="D243" t="s">
+        <v>33</v>
+      </c>
+      <c r="E243" t="s">
+        <v>504</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>507</v>
+      </c>
+      <c r="B244" t="s">
+        <v>66</v>
+      </c>
+      <c r="C244" t="s">
+        <v>510</v>
+      </c>
+      <c r="D244" t="s">
+        <v>102</v>
+      </c>
+      <c r="E244" t="s">
+        <v>508</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>511</v>
+      </c>
+      <c r="B245" t="s">
+        <v>67</v>
+      </c>
+      <c r="D245" t="s">
+        <v>409</v>
+      </c>
+      <c r="E245" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>513</v>
+      </c>
+      <c r="B246" t="s">
+        <v>65</v>
+      </c>
+      <c r="E246" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>515</v>
+      </c>
+      <c r="B247" t="s">
+        <v>336</v>
+      </c>
+      <c r="D247" t="s">
+        <v>102</v>
+      </c>
+      <c r="E247" t="s">
+        <v>10</v>
+      </c>
+      <c r="F247" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>541</v>
+      </c>
+      <c r="B248" t="s">
+        <v>65</v>
+      </c>
+      <c r="D248" t="s">
+        <v>22</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>609</v>
+      </c>
+      <c r="B249" t="s">
+        <v>74</v>
+      </c>
+      <c r="D249" t="s">
+        <v>27</v>
+      </c>
+      <c r="F249" s="1" t="s">
+        <v>610</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F205" r:id="rId1" xr:uid="{012D800E-0201-2140-BAF0-C0F42D34145F}"/>
-    <hyperlink ref="F206" r:id="rId2" xr:uid="{DB0C4B73-DA49-9945-9BF5-CC5F7E6A7A14}"/>
-    <hyperlink ref="F207" r:id="rId3" xr:uid="{F13E0DCE-4595-0B40-83B2-AC6A7465B91A}"/>
-    <hyperlink ref="F208" r:id="rId4" xr:uid="{43B9D480-C2B0-0041-ABD6-1DB5EDD4C305}"/>
-    <hyperlink ref="F210" r:id="rId5" xr:uid="{6587C4B8-319E-F643-9D7D-23EE72FB5B5A}"/>
-    <hyperlink ref="F144" r:id="rId6" xr:uid="{CA30899C-5E6D-7B40-A27F-B79530E60FE4}"/>
-    <hyperlink ref="F211" r:id="rId7" xr:uid="{F54D9AC5-E783-FD48-AEDF-6FB431BCF8AA}"/>
-    <hyperlink ref="F212" r:id="rId8" xr:uid="{179E013E-BA89-4845-9414-B6182D664816}"/>
-    <hyperlink ref="F174" r:id="rId9" xr:uid="{2FAE861D-AC4E-064F-B7E2-6474F1728692}"/>
-    <hyperlink ref="F196" r:id="rId10" xr:uid="{C653A051-6E1D-2548-96DE-1F1B9232D28A}"/>
-    <hyperlink ref="F215" r:id="rId11" xr:uid="{0CBA1BEA-A232-4D4E-86EF-CC9271B62F98}"/>
-    <hyperlink ref="F217" r:id="rId12" xr:uid="{9C4404D3-FCD2-0544-A6C1-BF3AE0854FC0}"/>
-    <hyperlink ref="F220" r:id="rId13" xr:uid="{7290BBD3-0EEB-DE4C-A99F-0FF66C9D941C}"/>
+    <hyperlink ref="F205" r:id="rId1" xr:uid="{07422E76-963D-BE4C-91D2-74761D746AB1}"/>
+    <hyperlink ref="F206" r:id="rId2" xr:uid="{C8604BFE-AFA2-924D-8C9A-6FCE798DA7E2}"/>
+    <hyperlink ref="F207" r:id="rId3" xr:uid="{15FEB7BF-6359-3945-AB94-AB7242E900B8}"/>
+    <hyperlink ref="F208" r:id="rId4" xr:uid="{5D40DEA3-AA18-C94F-9F06-80D92B21DD49}"/>
+    <hyperlink ref="F210" r:id="rId5" xr:uid="{1009D88F-A982-C448-8EB6-307D90E7AF42}"/>
+    <hyperlink ref="F144" r:id="rId6" xr:uid="{6E4032B1-A551-B442-AEFB-54DD405308C6}"/>
+    <hyperlink ref="F211" r:id="rId7" xr:uid="{8118E663-D536-B748-9645-E358EFE287ED}"/>
+    <hyperlink ref="F212" r:id="rId8" xr:uid="{51B43DF0-F329-8D42-8A3E-2F160CB4518E}"/>
+    <hyperlink ref="F174" r:id="rId9" xr:uid="{B09ECFBC-39E7-564C-BA8A-0926C18E813D}"/>
+    <hyperlink ref="F196" r:id="rId10" xr:uid="{5E414A40-C9A2-8644-8726-11CE20030288}"/>
+    <hyperlink ref="F215" r:id="rId11" xr:uid="{0CDC73E7-59D5-C947-A4E9-FE85ECE1631A}"/>
+    <hyperlink ref="F217" r:id="rId12" xr:uid="{3AFF515D-AAF2-BC4E-905C-06A21BFD793E}"/>
+    <hyperlink ref="F220" r:id="rId13" xr:uid="{A4E6E2A6-7946-9C4B-BC9A-78DCE667A493}"/>
+    <hyperlink ref="F247" r:id="rId14" xr:uid="{DA244133-494E-1547-BB85-0D376BEFECC9}"/>
+    <hyperlink ref="F243" r:id="rId15" xr:uid="{D923297B-DE03-4140-851F-1A112F3B8988}"/>
+    <hyperlink ref="F244" r:id="rId16" xr:uid="{0B903A3E-53FC-2D4E-A18B-F92AB8B1CAF9}"/>
+    <hyperlink ref="F229" r:id="rId17" xr:uid="{7D8058CB-50B6-3F4D-96FF-8A8E7BA8DAC5}"/>
+    <hyperlink ref="F239" r:id="rId18" xr:uid="{68A3A1F9-EA96-8543-AA1F-9994C62DCE60}"/>
+    <hyperlink ref="F193" r:id="rId19" xr:uid="{54AE62EB-C052-2B41-8749-ED3F5DDD696B}"/>
+    <hyperlink ref="F2" r:id="rId20" xr:uid="{D76E0D7F-D61F-414D-A906-B9DAAA81A89C}"/>
+    <hyperlink ref="F4" r:id="rId21" xr:uid="{AFA2CD13-6C84-BA47-807C-EEB58262A969}"/>
+    <hyperlink ref="F6" r:id="rId22" xr:uid="{B9B77B1C-F6D5-1E46-8FFE-293746C78183}"/>
+    <hyperlink ref="F7" r:id="rId23" xr:uid="{59D0D1A4-1F98-EC4A-BBF1-B736E4AD0035}"/>
+    <hyperlink ref="F10" r:id="rId24" xr:uid="{628EA24E-6C1E-9A40-92F5-EF33CDB1A0FA}"/>
+    <hyperlink ref="F11" r:id="rId25" xr:uid="{C5F84434-2C29-5B4F-8FB5-7EDF98411B5B}"/>
+    <hyperlink ref="F12" r:id="rId26" xr:uid="{BAE601E1-14A7-9741-9D0C-9D9622CF50D8}"/>
+    <hyperlink ref="F13" r:id="rId27" xr:uid="{5F908A7C-E198-C042-8350-C1392A16A0B2}"/>
+    <hyperlink ref="F14" r:id="rId28" xr:uid="{C776A94D-6D97-174B-AE7F-E3F193374044}"/>
+    <hyperlink ref="F15" r:id="rId29" xr:uid="{A9255562-6F1E-984A-B512-680F9EE7EE0F}"/>
+    <hyperlink ref="F17" r:id="rId30" xr:uid="{718574C4-0925-2943-B2C1-AB64A3974959}"/>
+    <hyperlink ref="F18" r:id="rId31" xr:uid="{29A65DD0-6F00-CA44-B8C0-0F1FE504D654}"/>
+    <hyperlink ref="G18" r:id="rId32" xr:uid="{4650FCE4-0E12-924B-A24B-9D47DD7F0190}"/>
+    <hyperlink ref="F21" r:id="rId33" xr:uid="{80E050BE-D5F8-6946-A2C4-EE8C215E29BB}"/>
+    <hyperlink ref="F29" r:id="rId34" xr:uid="{C59DDC8A-FB31-AF4E-A404-6A4BEC81AC55}"/>
+    <hyperlink ref="F33" r:id="rId35" xr:uid="{724EBD5D-00E0-984C-9D8A-D0ECCFCA579C}"/>
+    <hyperlink ref="F36" r:id="rId36" xr:uid="{F4E8700B-85DF-1A49-A3E8-0D15BD356A2E}"/>
+    <hyperlink ref="F38" r:id="rId37" xr:uid="{386D63C4-F6CC-664B-8FFC-3925FF1AFCB4}"/>
+    <hyperlink ref="F248" r:id="rId38" xr:uid="{9D3D60F8-1007-8046-81CB-E28BFD10ACEC}"/>
+    <hyperlink ref="F39" r:id="rId39" xr:uid="{415B5133-F8E1-564A-8C94-5DC4EB43FEC7}"/>
+    <hyperlink ref="F40" r:id="rId40" xr:uid="{D79032A2-4BBF-AD49-B3BD-AEA7CDBC8940}"/>
+    <hyperlink ref="F42" r:id="rId41" xr:uid="{ACCD8A61-57EF-C844-AB23-139C019AC6D8}"/>
+    <hyperlink ref="F43" r:id="rId42" xr:uid="{CF45310B-F8A5-AB4C-AC05-33576CD6E0C2}"/>
+    <hyperlink ref="F44" r:id="rId43" xr:uid="{5F0E93A6-3995-0841-894A-D95B36156972}"/>
+    <hyperlink ref="F45" r:id="rId44" xr:uid="{9FFDA17F-5297-9B48-B0CE-3572E5A2DA00}"/>
+    <hyperlink ref="F46" r:id="rId45" xr:uid="{D9ED18B3-1052-2C42-A151-F89AE4BCC125}"/>
+    <hyperlink ref="F47" r:id="rId46" xr:uid="{3E0FA73D-087A-DA43-A82C-FBA26CB522CD}"/>
+    <hyperlink ref="F48" r:id="rId47" xr:uid="{E2FF4251-91E8-0847-BD58-09A3B36FBE62}"/>
+    <hyperlink ref="F49" r:id="rId48" xr:uid="{816386B2-54A6-7D42-B6BF-EAE4FC021FEF}"/>
+    <hyperlink ref="G50" r:id="rId49" xr:uid="{C2D95B51-0A82-0F40-ADD1-4A95E3CDDDA8}"/>
+    <hyperlink ref="F50" r:id="rId50" xr:uid="{36343EFC-D5D7-9A47-87B8-4CFCDF074F13}"/>
+    <hyperlink ref="F51" r:id="rId51" xr:uid="{D81CF48F-9499-5F42-8225-10DF353BCC0E}"/>
+    <hyperlink ref="F53" r:id="rId52" xr:uid="{06761449-60F1-C344-8B0A-887ED9F8EAED}"/>
+    <hyperlink ref="F54" r:id="rId53" xr:uid="{0F225C2C-9268-D841-9F2B-31036E7B1123}"/>
+    <hyperlink ref="F55" r:id="rId54" xr:uid="{0A404919-2EE1-F345-AA02-50FC466D7F9F}"/>
+    <hyperlink ref="F57" r:id="rId55" xr:uid="{B3D7B37F-8332-A44B-9F81-F0FFFCEE3DD0}"/>
+    <hyperlink ref="F58" r:id="rId56" xr:uid="{9F1F69E8-423E-984E-ADA3-3DE5BE3134C0}"/>
+    <hyperlink ref="F59" r:id="rId57" xr:uid="{726D4034-584E-6446-AB9E-4DFE3CBA0F59}"/>
+    <hyperlink ref="F60" r:id="rId58" xr:uid="{D6780B22-1B01-4A46-8B10-FB1E4ADB8A95}"/>
+    <hyperlink ref="F61" r:id="rId59" xr:uid="{A8BE8568-B545-564D-9319-2823B84E48BB}"/>
+    <hyperlink ref="F62" r:id="rId60" xr:uid="{9C31AA73-5CF0-904D-BC94-AF88E2218281}"/>
+    <hyperlink ref="F63" r:id="rId61" xr:uid="{BA3FDB3E-77F0-CD4D-86EA-69645044F00D}"/>
+    <hyperlink ref="F64" r:id="rId62" xr:uid="{60EFDE0E-0435-2C48-9C83-AD4165BDCC2C}"/>
+    <hyperlink ref="F65" r:id="rId63" xr:uid="{E014E267-3C0F-1F43-9EE3-BC0BE04E350B}"/>
+    <hyperlink ref="F66" r:id="rId64" xr:uid="{0186954F-AA05-9645-98A9-7B3FE5497A57}"/>
+    <hyperlink ref="F67" r:id="rId65" xr:uid="{0DEEBEA3-83F9-2240-99EE-D48A1900425B}"/>
+    <hyperlink ref="F68" r:id="rId66" xr:uid="{1083A858-FC08-B84E-9F48-F9BB3CC88C64}"/>
+    <hyperlink ref="F69" r:id="rId67" xr:uid="{FAC558DB-4280-1244-8BA8-9552CA761496}"/>
+    <hyperlink ref="F71" r:id="rId68" xr:uid="{EBD6724E-B78D-7C4F-BBD6-7171DA547B87}"/>
+    <hyperlink ref="F72" r:id="rId69" xr:uid="{B0F6E293-90B9-0047-9821-D1024A319FAE}"/>
+    <hyperlink ref="F73" r:id="rId70" xr:uid="{565DD5B4-8E50-2D46-8102-6383B8FC3733}"/>
+    <hyperlink ref="F74" r:id="rId71" xr:uid="{BBE2E403-636E-1C42-ABFF-A190A8F007DF}"/>
+    <hyperlink ref="F75" r:id="rId72" xr:uid="{4A546DA1-78D8-0547-A6B3-E5E2AF439D65}"/>
+    <hyperlink ref="F76" r:id="rId73" xr:uid="{929EC5FA-637D-804E-A11B-0AE23DAC716A}"/>
+    <hyperlink ref="F77" r:id="rId74" xr:uid="{74F0A0EC-A813-014C-BFE5-5542A6B0FDCF}"/>
+    <hyperlink ref="F78" r:id="rId75" xr:uid="{9B9E0938-86D5-A34B-BF9D-81FDE9461EF4}"/>
+    <hyperlink ref="G80" r:id="rId76" xr:uid="{D769432E-407E-C24A-8D2B-500A64BED915}"/>
+    <hyperlink ref="F80" r:id="rId77" xr:uid="{FC9D99A7-68AA-FB46-A384-3BAD2E2606F4}"/>
+    <hyperlink ref="F83" r:id="rId78" xr:uid="{B7640A55-55EE-7141-9886-F5D4D5A93394}"/>
+    <hyperlink ref="F85" r:id="rId79" xr:uid="{40C2C3B4-A66C-534C-81A9-A815FDCBBFCD}"/>
+    <hyperlink ref="F86" r:id="rId80" xr:uid="{671E16E1-B054-0E47-8AAB-56388E694F8C}"/>
+    <hyperlink ref="F87" r:id="rId81" xr:uid="{B1FA52E8-2473-0A43-85C0-B677183243D2}"/>
+    <hyperlink ref="F89" r:id="rId82" xr:uid="{52CFFB80-CBC0-F343-87E8-A5DD8314641F}"/>
+    <hyperlink ref="F90" r:id="rId83" xr:uid="{5407802C-4F18-4F4C-AF50-F9608487A62A}"/>
+    <hyperlink ref="F92" r:id="rId84" xr:uid="{B86C8734-6C4E-E34C-975D-16A0D0B1BB1F}"/>
+    <hyperlink ref="F94" r:id="rId85" xr:uid="{D76F8BEE-FE2E-764F-872A-64E8B8C792C3}"/>
+    <hyperlink ref="G67" r:id="rId86" xr:uid="{31A7EEDA-0D4A-8E4C-BC6B-A919E6C738E4}"/>
+    <hyperlink ref="F95" r:id="rId87" xr:uid="{88839869-C23C-FB4F-A49D-097798AED316}"/>
+    <hyperlink ref="G95" r:id="rId88" xr:uid="{E8E08FBA-BD3F-D04E-ABDB-424E0CA14CFA}"/>
+    <hyperlink ref="F249" r:id="rId89" xr:uid="{0DE00517-7819-0F48-B135-EE0B8DC0F7D3}"/>
+    <hyperlink ref="F96" r:id="rId90" xr:uid="{3B312D5C-6B84-6A46-9D68-40C5E4A645F0}"/>
+    <hyperlink ref="F97" r:id="rId91" xr:uid="{AB9A8E36-B503-4F4E-83FF-117A1D77639D}"/>
+    <hyperlink ref="F100" r:id="rId92" xr:uid="{0A17F6FF-B834-CC47-8B53-020B285A4CDD}"/>
+    <hyperlink ref="F101" r:id="rId93" xr:uid="{F663CFFF-E612-AA49-8553-18D8690A8C99}"/>
+    <hyperlink ref="F103" r:id="rId94" xr:uid="{75DEBAEC-5A87-D64D-BAF0-6362D594DAEB}"/>
+    <hyperlink ref="F104" r:id="rId95" xr:uid="{6D792E84-B354-C94F-BC4D-63CB65CE315D}"/>
   </hyperlinks>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
